--- a/new start 2/data/EMS_temp_sensor (1).xlsx
+++ b/new start 2/data/EMS_temp_sensor (1).xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Workplace\NIT JSR\PhD\PhD\Sem 6\Review Work\RMSE calculation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0FDD932-4A3D-4E23-BD70-CB4EDC76C2CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01DDD90F-46AE-4D44-8F72-38A4A000614C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="EMS Sensors_Temp" sheetId="4" r:id="rId1"/>
+    <sheet name="EMS Sensors_Temp" sheetId="5" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -24,8 +24,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -48,7 +46,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -64,6 +62,12 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -73,7 +77,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -81,23 +85,41 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="21" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="21" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -401,437 +423,611 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:C41"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C8404E8F-C27C-48EE-A382-FA1B40B128D6}">
+  <dimension ref="A1:C54"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="31.109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.77734375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="34.44140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="33.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.109375" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="4" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" s="4">
-        <v>0.67401620370370374</v>
-      </c>
-      <c r="B2" s="1">
-        <v>33.1</v>
-      </c>
-      <c r="C2" s="1">
-        <v>33.299999999999997</v>
+      <c r="A2" s="5">
+        <v>0.28825231481481484</v>
+      </c>
+      <c r="B2" s="6">
+        <v>30.2</v>
+      </c>
+      <c r="C2" s="6">
+        <v>30.4</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" s="4">
-        <v>0.67413194444444446</v>
-      </c>
-      <c r="B3" s="1">
-        <v>33.1</v>
-      </c>
-      <c r="C3" s="1">
-        <v>33.200000000000003</v>
+      <c r="A3" s="5">
+        <v>0.28836805555555556</v>
+      </c>
+      <c r="B3" s="6">
+        <v>30.2</v>
+      </c>
+      <c r="C3" s="6">
+        <v>30.4</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" s="4">
-        <v>0.67424768518518519</v>
-      </c>
-      <c r="B4" s="1">
-        <v>33</v>
-      </c>
-      <c r="C4" s="1">
-        <v>33.299999999999997</v>
+      <c r="A4" s="5">
+        <v>0.28848379629629628</v>
+      </c>
+      <c r="B4" s="6">
+        <v>30.2</v>
+      </c>
+      <c r="C4" s="6">
+        <v>30.4</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" s="4">
-        <v>0.67436342592592602</v>
-      </c>
-      <c r="B5" s="1">
-        <v>33</v>
-      </c>
-      <c r="C5" s="1">
-        <v>33.200000000000003</v>
+      <c r="A5" s="5">
+        <v>0.288599537037037</v>
+      </c>
+      <c r="B5" s="6">
+        <v>30.3</v>
+      </c>
+      <c r="C5" s="6">
+        <v>30.4</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" s="4">
-        <v>0.67447916666666696</v>
-      </c>
-      <c r="B6" s="1">
-        <v>33</v>
-      </c>
-      <c r="C6" s="1">
-        <v>33.200000000000003</v>
+      <c r="A6" s="5">
+        <v>0.288715277777778</v>
+      </c>
+      <c r="B6" s="6">
+        <v>30.2</v>
+      </c>
+      <c r="C6" s="6">
+        <v>30.4</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" s="4">
-        <v>0.67459490740740702</v>
-      </c>
-      <c r="B7" s="1">
-        <v>33</v>
-      </c>
-      <c r="C7" s="1">
-        <v>33.5</v>
+      <c r="A7" s="5">
+        <v>0.288831018518518</v>
+      </c>
+      <c r="B7" s="6">
+        <v>30.3</v>
+      </c>
+      <c r="C7" s="6">
+        <v>30.4</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8" s="4">
-        <v>0.67471064814814796</v>
-      </c>
-      <c r="B8" s="1">
-        <v>33.1</v>
-      </c>
-      <c r="C8" s="1">
-        <v>33.4</v>
+      <c r="A8" s="5">
+        <v>0.288946759259259</v>
+      </c>
+      <c r="B8" s="6">
+        <v>30.3</v>
+      </c>
+      <c r="C8" s="6">
+        <v>30.4</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9" s="4">
-        <v>0.67482638888888902</v>
-      </c>
-      <c r="B9" s="1">
-        <v>33.1</v>
-      </c>
-      <c r="C9" s="1">
-        <v>33</v>
+      <c r="A9" s="5">
+        <v>0.2890625</v>
+      </c>
+      <c r="B9" s="6">
+        <v>30.3</v>
+      </c>
+      <c r="C9" s="6">
+        <v>30.4</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A10" s="4">
-        <v>0.67494212962962996</v>
-      </c>
-      <c r="B10" s="1">
-        <v>33.200000000000003</v>
-      </c>
-      <c r="C10" s="1">
-        <v>33.299999999999997</v>
+      <c r="A10" s="5">
+        <v>0.289178240740741</v>
+      </c>
+      <c r="B10" s="6">
+        <v>30.3</v>
+      </c>
+      <c r="C10" s="6">
+        <v>30.5</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A11" s="4">
-        <v>0.67505787037037002</v>
-      </c>
-      <c r="B11" s="1">
-        <v>33.200000000000003</v>
-      </c>
-      <c r="C11" s="1">
-        <v>33.299999999999997</v>
+      <c r="A11" s="5">
+        <v>0.289293981481481</v>
+      </c>
+      <c r="B11" s="6">
+        <v>30.3</v>
+      </c>
+      <c r="C11" s="6">
+        <v>30.5</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A12" s="4">
-        <v>0.67517361111111096</v>
-      </c>
-      <c r="B12" s="1">
-        <v>33.1</v>
-      </c>
-      <c r="C12" s="1">
-        <v>33.200000000000003</v>
+      <c r="A12" s="5">
+        <v>0.289409722222222</v>
+      </c>
+      <c r="B12" s="6">
+        <v>30.3</v>
+      </c>
+      <c r="C12" s="6">
+        <v>30.5</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A13" s="4">
-        <v>0.67528935185185202</v>
-      </c>
-      <c r="B13" s="1">
-        <v>33.200000000000003</v>
-      </c>
-      <c r="C13" s="1">
-        <v>33.200000000000003</v>
+      <c r="A13" s="5">
+        <v>0.289525462962963</v>
+      </c>
+      <c r="B13" s="6">
+        <v>30.3</v>
+      </c>
+      <c r="C13" s="6">
+        <v>30.5</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A14" s="4">
-        <v>0.67540509259259196</v>
-      </c>
-      <c r="B14" s="1">
-        <v>33.1</v>
-      </c>
-      <c r="C14" s="1">
-        <v>33.299999999999997</v>
+      <c r="A14" s="5">
+        <v>0.289641203703703</v>
+      </c>
+      <c r="B14" s="6">
+        <v>30.3</v>
+      </c>
+      <c r="C14" s="6">
+        <v>30.6</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A15" s="4">
-        <v>0.67552083333333302</v>
-      </c>
-      <c r="B15" s="1">
-        <v>33.1</v>
-      </c>
-      <c r="C15" s="1">
-        <v>33.299999999999997</v>
+      <c r="A15" s="5">
+        <v>0.289756944444444</v>
+      </c>
+      <c r="B15" s="6">
+        <v>30.4</v>
+      </c>
+      <c r="C15" s="6">
+        <v>30.6</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A16" s="4">
-        <v>0.67563657407407396</v>
-      </c>
-      <c r="B16" s="1">
-        <v>33</v>
-      </c>
-      <c r="C16" s="1">
-        <v>33.200000000000003</v>
+      <c r="A16" s="5">
+        <v>0.289872685185185</v>
+      </c>
+      <c r="B16" s="6">
+        <v>30.4</v>
+      </c>
+      <c r="C16" s="6">
+        <v>30.6</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A17" s="4">
-        <v>0.67575231481481501</v>
-      </c>
-      <c r="B17" s="1">
-        <v>33</v>
-      </c>
-      <c r="C17" s="1">
-        <v>33.200000000000003</v>
+      <c r="A17" s="5">
+        <v>0.289988425925926</v>
+      </c>
+      <c r="B17" s="6">
+        <v>30.4</v>
+      </c>
+      <c r="C17" s="6">
+        <v>30.6</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A18" s="4">
-        <v>0.67586805555555496</v>
-      </c>
-      <c r="B18" s="1">
-        <v>33</v>
-      </c>
-      <c r="C18" s="1">
-        <v>33.200000000000003</v>
+      <c r="A18" s="5">
+        <v>0.290104166666666</v>
+      </c>
+      <c r="B18" s="6">
+        <v>30.4</v>
+      </c>
+      <c r="C18" s="6">
+        <v>30.6</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A19" s="4">
-        <v>0.67598379629629601</v>
-      </c>
-      <c r="B19" s="1">
-        <v>33</v>
-      </c>
-      <c r="C19" s="1">
-        <v>33.6</v>
+      <c r="A19" s="5">
+        <v>0.290219907407407</v>
+      </c>
+      <c r="B19" s="6">
+        <v>30.4</v>
+      </c>
+      <c r="C19" s="6">
+        <v>30.6</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A20" s="4">
-        <v>0.67609953703703696</v>
-      </c>
-      <c r="B20" s="1">
-        <v>33</v>
-      </c>
-      <c r="C20" s="1">
-        <v>33.5</v>
+      <c r="A20" s="5">
+        <v>0.290335648148148</v>
+      </c>
+      <c r="B20" s="6">
+        <v>30.4</v>
+      </c>
+      <c r="C20" s="6">
+        <v>30.6</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A21" s="4">
-        <v>0.67621527777777701</v>
-      </c>
-      <c r="B21" s="1">
-        <v>33</v>
-      </c>
-      <c r="C21" s="1">
-        <v>33.299999999999997</v>
+      <c r="A21" s="5">
+        <v>0.29045138888888899</v>
+      </c>
+      <c r="B21" s="6">
+        <v>30.4</v>
+      </c>
+      <c r="C21" s="6">
+        <v>30.6</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A22" s="4">
-        <v>0.67633101851851796</v>
-      </c>
-      <c r="B22" s="1">
-        <v>33</v>
-      </c>
-      <c r="C22" s="1">
-        <v>33.4</v>
+      <c r="A22" s="5">
+        <v>0.290567129629629</v>
+      </c>
+      <c r="B22" s="6">
+        <v>30.4</v>
+      </c>
+      <c r="C22" s="6">
+        <v>30.6</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A23" s="4">
-        <v>0.67644675925925901</v>
-      </c>
-      <c r="B23" s="1">
-        <v>33</v>
-      </c>
-      <c r="C23" s="1">
-        <v>33.299999999999997</v>
+      <c r="A23" s="5">
+        <v>0.29068287037036999</v>
+      </c>
+      <c r="B23" s="6">
+        <v>30.4</v>
+      </c>
+      <c r="C23" s="6">
+        <v>30.6</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A24" s="4">
-        <v>0.67656249999999996</v>
-      </c>
-      <c r="B24" s="1">
-        <v>33</v>
-      </c>
-      <c r="C24" s="1">
-        <v>33</v>
+      <c r="A24" s="5">
+        <v>0.29079861111111099</v>
+      </c>
+      <c r="B24" s="6">
+        <v>30.4</v>
+      </c>
+      <c r="C24" s="6">
+        <v>30.6</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A25" s="4">
-        <v>0.67667824074074001</v>
-      </c>
-      <c r="B25" s="1">
-        <v>32.799999999999997</v>
-      </c>
-      <c r="C25" s="1">
-        <v>32.9</v>
+      <c r="A25" s="5">
+        <v>0.29091435185185099</v>
+      </c>
+      <c r="B25" s="6">
+        <v>30.3</v>
+      </c>
+      <c r="C25" s="6">
+        <v>30.4</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A26" s="4">
-        <v>0.67679398148148096</v>
-      </c>
-      <c r="B26" s="1">
-        <v>32.799999999999997</v>
-      </c>
-      <c r="C26" s="1">
-        <v>33.299999999999997</v>
+      <c r="A26" s="5">
+        <v>0.29103009259259199</v>
+      </c>
+      <c r="B26" s="6">
+        <v>30.3</v>
+      </c>
+      <c r="C26" s="6">
+        <v>30.4</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A27" s="4">
-        <v>0.67690972222222201</v>
-      </c>
-      <c r="B27" s="1">
-        <v>32.799999999999997</v>
-      </c>
-      <c r="C27" s="1">
-        <v>33.299999999999997</v>
+      <c r="A27" s="5">
+        <v>0.29114583333333299</v>
+      </c>
+      <c r="B27" s="6">
+        <v>30.3</v>
+      </c>
+      <c r="C27" s="6">
+        <v>30.4</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A28" s="4">
-        <v>0.67702546296296295</v>
-      </c>
-      <c r="B28" s="1">
-        <v>32.799999999999997</v>
-      </c>
-      <c r="C28" s="1">
-        <v>33.200000000000003</v>
+      <c r="A28" s="5">
+        <v>0.29126157407407399</v>
+      </c>
+      <c r="B28" s="6">
+        <v>30.3</v>
+      </c>
+      <c r="C28" s="6">
+        <v>30.4</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A29" s="4">
-        <v>0.67714120370370301</v>
-      </c>
-      <c r="B29" s="1">
-        <v>32.799999999999997</v>
-      </c>
-      <c r="C29" s="1">
-        <v>33.200000000000003</v>
+      <c r="A29" s="5">
+        <v>0.29137731481481399</v>
+      </c>
+      <c r="B29" s="6">
+        <v>30.3</v>
+      </c>
+      <c r="C29" s="6">
+        <v>30.4</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A30" s="4">
-        <v>0.67725694444444395</v>
-      </c>
-      <c r="B30" s="1">
-        <v>32.799999999999997</v>
-      </c>
-      <c r="C30" s="1">
-        <v>33.299999999999997</v>
+      <c r="A30" s="5">
+        <v>0.29149305555555499</v>
+      </c>
+      <c r="B30" s="6">
+        <v>30.2</v>
+      </c>
+      <c r="C30" s="6">
+        <v>30.4</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A31" s="4">
-        <v>0.67737268518518501</v>
-      </c>
-      <c r="B31" s="1">
-        <v>32.799999999999997</v>
-      </c>
-      <c r="C31" s="1">
-        <v>33.299999999999997</v>
+      <c r="A31" s="5">
+        <v>0.29160879629629599</v>
+      </c>
+      <c r="B31" s="6">
+        <v>30.3</v>
+      </c>
+      <c r="C31" s="6">
+        <v>30.4</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A32" s="4">
-        <v>0.67748842592592495</v>
-      </c>
-      <c r="B32" s="1">
-        <v>32.799999999999997</v>
-      </c>
-      <c r="C32" s="1">
-        <v>33.200000000000003</v>
+      <c r="A32" s="5">
+        <v>0.29172453703703599</v>
+      </c>
+      <c r="B32" s="6">
+        <v>30.3</v>
+      </c>
+      <c r="C32" s="6">
+        <v>30.4</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A33" s="4">
-        <v>0.67760416666666601</v>
-      </c>
-      <c r="B33" s="1">
-        <v>32.799999999999997</v>
-      </c>
-      <c r="C33" s="1">
-        <v>33.200000000000003</v>
+      <c r="A33" s="5">
+        <v>0.29184027777777699</v>
+      </c>
+      <c r="B33" s="6">
+        <v>30.3</v>
+      </c>
+      <c r="C33" s="6">
+        <v>30.4</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A34" s="4">
-        <v>0.67771990740740695</v>
-      </c>
-      <c r="B34" s="1">
-        <v>32.9</v>
-      </c>
-      <c r="C34" s="1">
-        <v>33.200000000000003</v>
+      <c r="A34" s="5">
+        <v>0.29195601851851799</v>
+      </c>
+      <c r="B34" s="6">
+        <v>30.3</v>
+      </c>
+      <c r="C34" s="6">
+        <v>30.4</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A35" s="4">
-        <v>0.67783564814814801</v>
-      </c>
-      <c r="B35" s="1">
-        <v>33</v>
-      </c>
-      <c r="C35" s="1">
-        <v>33.6</v>
+      <c r="A35" s="5">
+        <v>0.29207175925925899</v>
+      </c>
+      <c r="B35" s="6">
+        <v>30.3</v>
+      </c>
+      <c r="C35" s="6">
+        <v>30.4</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A36" s="4">
-        <v>0.67795138888888795</v>
-      </c>
-      <c r="B36" s="1">
-        <v>33.1</v>
-      </c>
-      <c r="C36" s="1">
-        <v>33.5</v>
+      <c r="A36" s="5">
+        <v>0.29218749999999899</v>
+      </c>
+      <c r="B36" s="6">
+        <v>30.3</v>
+      </c>
+      <c r="C36" s="6">
+        <v>30.4</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A37" s="4">
-        <v>0.67806712962962901</v>
-      </c>
-      <c r="B37" s="1">
-        <v>33.1</v>
-      </c>
-      <c r="C37" s="1">
-        <v>33.299999999999997</v>
+      <c r="A37" s="5">
+        <v>0.29230324074073999</v>
+      </c>
+      <c r="B37" s="6">
+        <v>30.2</v>
+      </c>
+      <c r="C37" s="6">
+        <v>30.5</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C38" s="1"/>
+      <c r="A38" s="5">
+        <v>0.29241898148148099</v>
+      </c>
+      <c r="B38" s="6">
+        <v>30.3</v>
+      </c>
+      <c r="C38" s="6">
+        <v>30.5</v>
+      </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C39" s="1"/>
+      <c r="A39" s="5">
+        <v>0.29253472222222199</v>
+      </c>
+      <c r="B39" s="6">
+        <v>30.3</v>
+      </c>
+      <c r="C39" s="6">
+        <v>30.5</v>
+      </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C40" s="1"/>
+      <c r="A40" s="5">
+        <v>0.29265046296296199</v>
+      </c>
+      <c r="B40" s="6">
+        <v>30.3</v>
+      </c>
+      <c r="C40" s="6">
+        <v>30.5</v>
+      </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C41" s="1"/>
+      <c r="A41" s="5">
+        <v>0.29276620370370299</v>
+      </c>
+      <c r="B41" s="6">
+        <v>30.3</v>
+      </c>
+      <c r="C41" s="6">
+        <v>30.5</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A42" s="5">
+        <v>0.29288194444444399</v>
+      </c>
+      <c r="B42" s="6">
+        <v>30.3</v>
+      </c>
+      <c r="C42" s="6">
+        <v>30.5</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A43" s="5">
+        <v>0.29299768518518399</v>
+      </c>
+      <c r="B43" s="6">
+        <v>30.3</v>
+      </c>
+      <c r="C43" s="6">
+        <v>30.5</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A44" s="5">
+        <v>0.29311342592592499</v>
+      </c>
+      <c r="B44" s="6">
+        <v>30.3</v>
+      </c>
+      <c r="C44" s="6">
+        <v>30.5</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A45" s="5">
+        <v>0.29322916666666599</v>
+      </c>
+      <c r="B45" s="6">
+        <v>30.3</v>
+      </c>
+      <c r="C45" s="6">
+        <v>30.5</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A46" s="5">
+        <v>0.29334490740740699</v>
+      </c>
+      <c r="B46" s="6">
+        <v>30.3</v>
+      </c>
+      <c r="C46" s="6">
+        <v>30.5</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A47" s="5">
+        <v>0.29346064814814699</v>
+      </c>
+      <c r="B47" s="6">
+        <v>30.3</v>
+      </c>
+      <c r="C47" s="6">
+        <v>30.5</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A48" s="5">
+        <v>0.29357638888888798</v>
+      </c>
+      <c r="B48" s="6">
+        <v>30.2</v>
+      </c>
+      <c r="C48" s="6">
+        <v>30.5</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A49" s="5">
+        <v>0.29369212962962898</v>
+      </c>
+      <c r="B49" s="6">
+        <v>30.3</v>
+      </c>
+      <c r="C49" s="6">
+        <v>30.5</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A50" s="5">
+        <v>0.29380787037036898</v>
+      </c>
+      <c r="B50" s="6">
+        <v>30.3</v>
+      </c>
+      <c r="C50" s="6">
+        <v>30.5</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A51" s="5">
+        <v>0.29392361111110998</v>
+      </c>
+      <c r="B51" s="6">
+        <v>30.3</v>
+      </c>
+      <c r="C51" s="6">
+        <v>30.5</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A52" s="5">
+        <v>0.29403935185185098</v>
+      </c>
+      <c r="B52" s="6">
+        <v>30.3</v>
+      </c>
+      <c r="C52" s="6">
+        <v>30.5</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A53" s="5">
+        <v>0.29415509259259198</v>
+      </c>
+      <c r="B53" s="6">
+        <v>30.3</v>
+      </c>
+      <c r="C53" s="6">
+        <v>30.5</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A54" s="5">
+        <v>0.29427083333333198</v>
+      </c>
+      <c r="B54" s="6">
+        <v>30.3</v>
+      </c>
+      <c r="C54" s="6">
+        <v>30.5</v>
+      </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>